--- a/docentes/Ortega Valle Manuel - Estadisticos 20212.xlsx
+++ b/docentes/Ortega Valle Manuel - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="61">
   <si>
     <t>Mat</t>
   </si>
@@ -85,16 +85,52 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>VASQUEZ</t>
   </si>
   <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
     <t>LEYVA</t>
   </si>
   <si>
     <t>REYES</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>MIXCOHUA</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>IXTLA</t>
+  </si>
+  <si>
+    <t>ZEPEDA</t>
+  </si>
+  <si>
+    <t>CARRASCO</t>
+  </si>
+  <si>
+    <t>TREJO</t>
   </si>
   <si>
     <t>VELAZQUEZ</t>
@@ -103,13 +139,67 @@
     <t>PEREZ</t>
   </si>
   <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>GALEOTE</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>PINO</t>
+  </si>
+  <si>
+    <t>ELIEL</t>
+  </si>
+  <si>
     <t>VICTOR MANUEL</t>
   </si>
   <si>
+    <t>OMAR ALDAIR</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>SAMANTHA</t>
+  </si>
+  <si>
+    <t>ZULEICA RENATA</t>
+  </si>
+  <si>
+    <t>CESAR</t>
+  </si>
+  <si>
     <t>ELIAN</t>
   </si>
   <si>
     <t>ARANTZA</t>
+  </si>
+  <si>
+    <t>CRISTIAN</t>
+  </si>
+  <si>
+    <t>ALEXIS</t>
+  </si>
+  <si>
+    <t>VALENTIN</t>
+  </si>
+  <si>
+    <t>KARLA DENISSE</t>
+  </si>
+  <si>
+    <t>RICARDO ISIDRO</t>
+  </si>
+  <si>
+    <t>CESAR JAHIR</t>
   </si>
 </sst>
 </file>
@@ -1034,7 +1124,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1066,16 +1156,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920382</v>
+        <v>20330051920345</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1089,22 +1179,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920298</v>
+        <v>20330051920382</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1112,25 +1202,301 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920310</v>
+        <v>19330050470596</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>20330051920301</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" t="s">
+        <v>49</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>20330051920309</v>
+      </c>
+      <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>20330051920379</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>19330051920263</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>20330051920298</v>
+      </c>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" t="s">
+        <v>53</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>20330051920310</v>
+      </c>
+      <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>19330051920433</v>
+      </c>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" t="s">
+        <v>55</v>
+      </c>
+      <c r="E11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>19330051920257</v>
+      </c>
+      <c r="B12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>19330051920266</v>
+      </c>
+      <c r="B13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" t="s">
+        <v>57</v>
+      </c>
+      <c r="E13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>19330051920406</v>
+      </c>
+      <c r="B14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>19330051920409</v>
+      </c>
+      <c r="B15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>19330051920411</v>
+      </c>
+      <c r="B16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" t="s">
+        <v>60</v>
+      </c>
+      <c r="E16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Ortega Valle Manuel - Estadisticos 20212.xlsx
+++ b/docentes/Ortega Valle Manuel - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="75">
   <si>
     <t>Mat</t>
   </si>
@@ -103,12 +103,24 @@
     <t>TORRES</t>
   </si>
   <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
     <t>LEYVA</t>
   </si>
   <si>
     <t>REYES</t>
   </si>
   <si>
+    <t>VALENCIA</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
@@ -121,6 +133,9 @@
     <t>SANCHEZ</t>
   </si>
   <si>
+    <t>OCTAVIANO</t>
+  </si>
+  <si>
     <t>IXTLA</t>
   </si>
   <si>
@@ -130,30 +145,39 @@
     <t>CARRASCO</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>GARATE</t>
+  </si>
+  <si>
+    <t>AVELINO</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>GALEOTE</t>
+  </si>
+  <si>
     <t>TREJO</t>
   </si>
   <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>GALEOTE</t>
-  </si>
-  <si>
     <t>IXMATLAHUA</t>
   </si>
   <si>
     <t>JUAREZ</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
     <t>PINO</t>
   </si>
   <si>
@@ -175,21 +199,36 @@
     <t>ZULEICA RENATA</t>
   </si>
   <si>
+    <t>IVAN</t>
+  </si>
+  <si>
+    <t>JAVIER FERNANDO</t>
+  </si>
+  <si>
+    <t>JOSUE</t>
+  </si>
+  <si>
+    <t>AXEL</t>
+  </si>
+  <si>
+    <t>ELIAN</t>
+  </si>
+  <si>
+    <t>ARANTZA</t>
+  </si>
+  <si>
+    <t>MAURICIO</t>
+  </si>
+  <si>
+    <t>CRISTIAN</t>
+  </si>
+  <si>
+    <t>ALEXIS</t>
+  </si>
+  <si>
     <t>CESAR</t>
   </si>
   <si>
-    <t>ELIAN</t>
-  </si>
-  <si>
-    <t>ARANTZA</t>
-  </si>
-  <si>
-    <t>CRISTIAN</t>
-  </si>
-  <si>
-    <t>ALEXIS</t>
-  </si>
-  <si>
     <t>VALENTIN</t>
   </si>
   <si>
@@ -200,6 +239,9 @@
   </si>
   <si>
     <t>CESAR JAHIR</t>
+  </si>
+  <si>
+    <t>JOSE ANTONIO</t>
   </si>
 </sst>
 </file>
@@ -1124,7 +1166,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1162,10 +1204,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1188,7 +1230,7 @@
         <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1211,7 +1253,7 @@
         <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1234,7 +1276,7 @@
         <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1254,10 +1296,10 @@
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1277,10 +1319,10 @@
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1294,22 +1336,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920263</v>
+        <v>19330051920040</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D8" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1317,91 +1359,91 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920298</v>
+        <v>19330051920258</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920310</v>
+        <v>19330051920094</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920433</v>
+        <v>19330051920105</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D11" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920257</v>
+        <v>20330051920298</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1409,22 +1451,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920266</v>
+        <v>20330051920310</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1432,22 +1474,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>19330051920406</v>
+        <v>19330051920037</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D14" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1455,16 +1497,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>19330051920409</v>
+        <v>19330051920433</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D15" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
@@ -1478,16 +1520,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>19330051920411</v>
+        <v>19330051920257</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C16" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D16" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
@@ -1496,6 +1538,144 @@
         <v>15</v>
       </c>
       <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>19330051920263</v>
+      </c>
+      <c r="B17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" t="s">
+        <v>50</v>
+      </c>
+      <c r="D17" t="s">
+        <v>69</v>
+      </c>
+      <c r="E17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>19330051920266</v>
+      </c>
+      <c r="B18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" t="s">
+        <v>70</v>
+      </c>
+      <c r="E18" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>19330051920406</v>
+      </c>
+      <c r="B19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" t="s">
+        <v>71</v>
+      </c>
+      <c r="E19" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>19330051920409</v>
+      </c>
+      <c r="B20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20" t="s">
+        <v>72</v>
+      </c>
+      <c r="E20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>19330051920411</v>
+      </c>
+      <c r="B21" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" t="s">
+        <v>53</v>
+      </c>
+      <c r="D21" t="s">
+        <v>73</v>
+      </c>
+      <c r="E21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" t="s">
+        <v>15</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>19330051920115</v>
+      </c>
+      <c r="B22" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D22" t="s">
+        <v>74</v>
+      </c>
+      <c r="E22" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" t="s">
+        <v>14</v>
+      </c>
+      <c r="G22">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Ortega Valle Manuel - Estadisticos 20212.xlsx
+++ b/docentes/Ortega Valle Manuel - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="84">
   <si>
     <t>Mat</t>
   </si>
@@ -88,100 +88,118 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
     <t>VASQUEZ</t>
   </si>
   <si>
     <t>VENTURA</t>
   </si>
   <si>
+    <t>ARROYO</t>
+  </si>
+  <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
+    <t>VALENCIA</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>MONSALVO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>LEYVA</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
     <t>RAMOS</t>
   </si>
   <si>
-    <t>TORRES</t>
-  </si>
-  <si>
     <t>VILLEGAS</t>
   </si>
   <si>
-    <t>CRUZ</t>
+    <t>GONZALEZ</t>
   </si>
   <si>
     <t>HERRERA</t>
   </si>
   <si>
-    <t>LEYVA</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>OCTAVIANO</t>
-  </si>
-  <si>
-    <t>IXTLA</t>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>CARRASCO</t>
+  </si>
+  <si>
+    <t>CHAVEZ</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>QUINTERO</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
   </si>
   <si>
     <t>ZEPEDA</t>
   </si>
   <si>
-    <t>CARRASCO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>GARATE</t>
-  </si>
-  <si>
-    <t>AVELINO</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
     <t>SERRANO</t>
   </si>
   <si>
     <t>GALEOTE</t>
   </si>
   <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
     <t>PINO</t>
   </si>
   <si>
-    <t>ELIEL</t>
+    <t>EDGAR DANIEL</t>
+  </si>
+  <si>
+    <t>JAHEL</t>
   </si>
   <si>
     <t>VICTOR MANUEL</t>
@@ -190,58 +208,67 @@
     <t>OMAR ALDAIR</t>
   </si>
   <si>
+    <t>CITLALLI</t>
+  </si>
+  <si>
+    <t>DANIEL</t>
+  </si>
+  <si>
     <t>VANESSA</t>
   </si>
   <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>ZULEICA RENATA</t>
+  </si>
+  <si>
+    <t>YAIR ANTONIO</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>NATANAEL</t>
+  </si>
+  <si>
+    <t>MAURICIO</t>
+  </si>
+  <si>
+    <t>ALEXANDER</t>
+  </si>
+  <si>
+    <t>ANGEL GERARDO</t>
+  </si>
+  <si>
+    <t>RICARDO ISIDRO</t>
+  </si>
+  <si>
+    <t>ARIAN ALEXIS</t>
+  </si>
+  <si>
+    <t>ELIAN</t>
+  </si>
+  <si>
+    <t>NAHOMY</t>
+  </si>
+  <si>
     <t>SAMANTHA</t>
   </si>
   <si>
-    <t>ZULEICA RENATA</t>
+    <t>ARANTZA</t>
   </si>
   <si>
     <t>IVAN</t>
   </si>
   <si>
-    <t>JAVIER FERNANDO</t>
-  </si>
-  <si>
-    <t>JOSUE</t>
-  </si>
-  <si>
-    <t>AXEL</t>
-  </si>
-  <si>
-    <t>ELIAN</t>
-  </si>
-  <si>
-    <t>ARANTZA</t>
-  </si>
-  <si>
-    <t>MAURICIO</t>
-  </si>
-  <si>
     <t>CRISTIAN</t>
   </si>
   <si>
     <t>ALEXIS</t>
   </si>
   <si>
-    <t>CESAR</t>
-  </si>
-  <si>
-    <t>VALENTIN</t>
-  </si>
-  <si>
-    <t>KARLA DENISSE</t>
-  </si>
-  <si>
-    <t>RICARDO ISIDRO</t>
-  </si>
-  <si>
     <t>CESAR JAHIR</t>
-  </si>
-  <si>
-    <t>JOSE ANTONIO</t>
   </si>
 </sst>
 </file>
@@ -668,19 +695,19 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G3">
-        <v>78.79000000000001</v>
+        <v>93.94</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -694,19 +721,19 @@
         <v>38</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>36</v>
+      </c>
+      <c r="G4">
+        <v>94.73999999999999</v>
+      </c>
+      <c r="H4">
         <v>7</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>31</v>
-      </c>
-      <c r="G4">
-        <v>81.58</v>
-      </c>
-      <c r="H4">
-        <v>7.3</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -720,19 +747,19 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G5">
-        <v>83.33</v>
+        <v>95.83</v>
       </c>
       <c r="H5">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -746,19 +773,19 @@
         <v>31</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G6">
-        <v>83.87</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -772,19 +799,19 @@
         <v>32</v>
       </c>
       <c r="D7">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F7">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="G7">
-        <v>56.25</v>
+        <v>81.25</v>
       </c>
       <c r="H7">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>
@@ -837,16 +864,19 @@
         <v>24</v>
       </c>
       <c r="D2">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>75</v>
+      </c>
+      <c r="H2">
+        <v>6.2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -860,16 +890,19 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>69.7</v>
+      </c>
+      <c r="H3">
+        <v>6.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -883,16 +916,19 @@
         <v>38</v>
       </c>
       <c r="D4">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>65.79000000000001</v>
+      </c>
+      <c r="H4">
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -906,16 +942,19 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>75</v>
+      </c>
+      <c r="H5">
+        <v>7.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -929,16 +968,19 @@
         <v>31</v>
       </c>
       <c r="D6">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>80.65000000000001</v>
+      </c>
+      <c r="H6">
+        <v>6.7</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -952,16 +994,19 @@
         <v>32</v>
       </c>
       <c r="D7">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>62.5</v>
+      </c>
+      <c r="H7">
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>
@@ -1017,13 +1062,13 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G2">
-        <v>70.83</v>
+        <v>75</v>
       </c>
       <c r="H2">
         <v>6.2</v>
@@ -1040,19 +1085,19 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G3">
-        <v>78.79000000000001</v>
+        <v>69.7</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1066,19 +1111,19 @@
         <v>38</v>
       </c>
       <c r="D4">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F4">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="G4">
-        <v>81.58</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="H4">
-        <v>7.3</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1092,19 +1137,19 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G5">
-        <v>83.33</v>
+        <v>75</v>
       </c>
       <c r="H5">
-        <v>7.3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1118,19 +1163,19 @@
         <v>31</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G6">
-        <v>83.87</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="H6">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1144,19 +1189,19 @@
         <v>32</v>
       </c>
       <c r="D7">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G7">
-        <v>56.25</v>
+        <v>62.5</v>
       </c>
       <c r="H7">
-        <v>6.9</v>
+        <v>6.3</v>
       </c>
     </row>
   </sheetData>
@@ -1166,7 +1211,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1198,16 +1243,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920345</v>
+        <v>20330051920381</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1221,16 +1266,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920382</v>
+        <v>20330051920354</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="D3" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1244,16 +1289,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330050470596</v>
+        <v>20330051920382</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1267,22 +1312,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920301</v>
+        <v>19330050470596</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1290,16 +1335,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920309</v>
+        <v>20330051920285</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1313,16 +1358,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920379</v>
+        <v>20330051920287</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D7" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1336,22 +1381,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920040</v>
+        <v>20330051920301</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1359,22 +1404,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920258</v>
+        <v>20330051920307</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1382,22 +1427,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920094</v>
+        <v>20330051920379</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D10" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1405,22 +1450,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920105</v>
+        <v>18330051920168</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1428,48 +1473,48 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920298</v>
+        <v>19330051920026</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D12" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920310</v>
+        <v>18330061460390</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D13" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1480,10 +1525,10 @@
         <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D14" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
@@ -1492,44 +1537,44 @@
         <v>12</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>19330051920433</v>
+        <v>19330051420227</v>
       </c>
       <c r="B15" t="s">
         <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D15" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G15">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>19330051920257</v>
+        <v>19330051920400</v>
       </c>
       <c r="B16" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D16" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
@@ -1538,21 +1583,21 @@
         <v>15</v>
       </c>
       <c r="G16">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>19330051920263</v>
+        <v>19330051920409</v>
       </c>
       <c r="B17" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D17" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
@@ -1561,50 +1606,50 @@
         <v>15</v>
       </c>
       <c r="G17">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>19330051920266</v>
+        <v>19330051920001</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D18" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E18" t="s">
         <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>19330051920406</v>
+        <v>20330051920298</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C19" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D19" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1612,22 +1657,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>19330051920409</v>
+        <v>19330051920208</v>
       </c>
       <c r="B20" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="D20" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E20" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1635,22 +1680,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>19330051920411</v>
+        <v>20330051920309</v>
       </c>
       <c r="B21" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C21" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D21" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="E21" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -1658,24 +1703,116 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>19330051920115</v>
+        <v>20330051920310</v>
       </c>
       <c r="B22" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C22" t="s">
+        <v>29</v>
+      </c>
+      <c r="D22" t="s">
+        <v>79</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" t="s">
+        <v>11</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>19330051920040</v>
+      </c>
+      <c r="B23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" t="s">
+        <v>49</v>
+      </c>
+      <c r="D23" t="s">
+        <v>80</v>
+      </c>
+      <c r="E23" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>19330051920433</v>
+      </c>
+      <c r="B24" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D24" t="s">
+        <v>81</v>
+      </c>
+      <c r="E24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" t="s">
+        <v>15</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>19330051920257</v>
+      </c>
+      <c r="B25" t="s">
         <v>22</v>
       </c>
-      <c r="D22" t="s">
-        <v>74</v>
-      </c>
-      <c r="E22" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" t="s">
-        <v>14</v>
-      </c>
-      <c r="G22">
+      <c r="C25" t="s">
+        <v>57</v>
+      </c>
+      <c r="D25" t="s">
+        <v>82</v>
+      </c>
+      <c r="E25" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25" t="s">
+        <v>15</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>19330051920411</v>
+      </c>
+      <c r="B26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C26" t="s">
+        <v>58</v>
+      </c>
+      <c r="D26" t="s">
+        <v>83</v>
+      </c>
+      <c r="E26" t="s">
+        <v>9</v>
+      </c>
+      <c r="F26" t="s">
+        <v>15</v>
+      </c>
+      <c r="G26">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Ortega Valle Manuel - Estadisticos 20212.xlsx
+++ b/docentes/Ortega Valle Manuel - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="86">
   <si>
     <t>Mat</t>
   </si>
@@ -103,97 +103,106 @@
     <t>CABRERA</t>
   </si>
   <si>
+    <t>LEYVA</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>VALENCIA</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>MONSALVO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
+    <t>CADEZA</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>MONSALVO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>LEYVA</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>CARRASCO</t>
+  </si>
+  <si>
+    <t>CHAVEZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
     <t>MORALES</t>
   </si>
   <si>
-    <t>CARRASCO</t>
-  </si>
-  <si>
-    <t>CHAVEZ</t>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>PALMA</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>GALEOTE</t>
+  </si>
+  <si>
+    <t>QUINTERO</t>
+  </si>
+  <si>
+    <t>PINO</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
   </si>
   <si>
     <t>CASTILLO</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>QUINTERO</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>ZEPEDA</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>GALEOTE</t>
-  </si>
-  <si>
-    <t>PINO</t>
+    <t>GALLARDO</t>
   </si>
   <si>
     <t>EDGAR DANIEL</t>
@@ -214,10 +223,10 @@
     <t>DANIEL</t>
   </si>
   <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
+    <t>ELIAN</t>
+  </si>
+  <si>
+    <t>ARANTZA</t>
   </si>
   <si>
     <t>ZULEICA RENATA</t>
@@ -229,46 +238,43 @@
     <t>ISRAEL</t>
   </si>
   <si>
+    <t>MAURICIO</t>
+  </si>
+  <si>
+    <t>IVAN</t>
+  </si>
+  <si>
+    <t>URIEL</t>
+  </si>
+  <si>
+    <t>ALEXANDER</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>CRISTIAN</t>
+  </si>
+  <si>
+    <t>ALEXIS</t>
+  </si>
+  <si>
+    <t>ANGEL GERARDO</t>
+  </si>
+  <si>
+    <t>CESAR JAHIR</t>
+  </si>
+  <si>
+    <t>ARIAN ALEXIS</t>
+  </si>
+  <si>
+    <t>NAHOMY</t>
+  </si>
+  <si>
     <t>NATANAEL</t>
   </si>
   <si>
-    <t>MAURICIO</t>
-  </si>
-  <si>
-    <t>ALEXANDER</t>
-  </si>
-  <si>
-    <t>ANGEL GERARDO</t>
-  </si>
-  <si>
-    <t>RICARDO ISIDRO</t>
-  </si>
-  <si>
-    <t>ARIAN ALEXIS</t>
-  </si>
-  <si>
-    <t>ELIAN</t>
-  </si>
-  <si>
-    <t>NAHOMY</t>
-  </si>
-  <si>
-    <t>SAMANTHA</t>
-  </si>
-  <si>
-    <t>ARANTZA</t>
-  </si>
-  <si>
-    <t>IVAN</t>
-  </si>
-  <si>
-    <t>CRISTIAN</t>
-  </si>
-  <si>
-    <t>ALEXIS</t>
-  </si>
-  <si>
-    <t>CESAR JAHIR</t>
+    <t>IRVING OTTONIEL</t>
   </si>
 </sst>
 </file>
@@ -1211,7 +1217,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1249,10 +1255,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1272,10 +1278,10 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1298,7 +1304,7 @@
         <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1318,10 +1324,10 @@
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="D5" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1341,10 +1347,10 @@
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="D6" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1364,10 +1370,10 @@
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1381,16 +1387,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920301</v>
+        <v>20330051920298</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="D8" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1404,16 +1410,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920307</v>
+        <v>20330051920310</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1433,10 +1439,10 @@
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D10" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1453,13 +1459,13 @@
         <v>18330051920168</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D11" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -1476,13 +1482,13 @@
         <v>19330051920026</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D12" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -1496,16 +1502,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>18330061460390</v>
+        <v>19330051920037</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D13" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -1519,16 +1525,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>19330051920037</v>
+        <v>19330051920040</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D14" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
@@ -1542,16 +1548,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>19330051420227</v>
+        <v>19330051920233</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D15" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
@@ -1565,22 +1571,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>19330051920400</v>
+        <v>19330051420227</v>
       </c>
       <c r="B16" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C16" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D16" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G16">
         <v>2</v>
@@ -1588,16 +1594,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>19330051920409</v>
+        <v>19330051920251</v>
       </c>
       <c r="B17" t="s">
         <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D17" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
@@ -1611,22 +1617,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>19330051920001</v>
+        <v>19330051920433</v>
       </c>
       <c r="B18" t="s">
         <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D18" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E18" t="s">
         <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G18">
         <v>2</v>
@@ -1634,114 +1640,114 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920298</v>
+        <v>19330051920257</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="C19" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D19" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E19" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F19" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G19">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>19330051920208</v>
+        <v>19330051920400</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D20" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E20" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F20" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G20">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>20330051920309</v>
+        <v>19330051920411</v>
       </c>
       <c r="B21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C21" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D21" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E21" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F21" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G21">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>20330051920310</v>
+        <v>19330051920001</v>
       </c>
       <c r="B22" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C22" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="D22" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E22" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F22" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G22">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>19330051920040</v>
+        <v>19330051920208</v>
       </c>
       <c r="B23" t="s">
         <v>41</v>
       </c>
       <c r="C23" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="D23" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E23" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -1749,22 +1755,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>19330051920433</v>
+        <v>18330061460390</v>
       </c>
       <c r="B24" t="s">
         <v>42</v>
       </c>
       <c r="C24" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D24" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E24" t="s">
         <v>9</v>
       </c>
       <c r="F24" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1772,47 +1778,24 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>19330051920257</v>
+        <v>19330051920088</v>
       </c>
       <c r="B25" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="C25" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D25" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E25" t="s">
         <v>9</v>
       </c>
       <c r="F25" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>19330051920411</v>
-      </c>
-      <c r="B26" t="s">
-        <v>36</v>
-      </c>
-      <c r="C26" t="s">
-        <v>58</v>
-      </c>
-      <c r="D26" t="s">
-        <v>83</v>
-      </c>
-      <c r="E26" t="s">
-        <v>9</v>
-      </c>
-      <c r="F26" t="s">
-        <v>15</v>
-      </c>
-      <c r="G26">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Ortega Valle Manuel - Estadisticos 20212.xlsx
+++ b/docentes/Ortega Valle Manuel - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="42">
   <si>
     <t>Mat</t>
   </si>
@@ -85,25 +85,19 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>ARROYO</t>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>BONILLA</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
   </si>
   <si>
     <t>CABRERA</t>
   </si>
   <si>
-    <t>LEYVA</t>
+    <t>HERRERA</t>
   </si>
   <si>
     <t>REYES</t>
@@ -112,169 +106,43 @@
     <t>TORRES</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
     <t>PEREZ</t>
   </si>
   <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>MONSALVO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>CADEZA</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
     <t>CARRASCO</t>
   </si>
   <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>PALMA</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>GALEOTE</t>
-  </si>
-  <si>
-    <t>QUINTERO</t>
-  </si>
-  <si>
-    <t>PINO</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>EDGAR DANIEL</t>
-  </si>
-  <si>
-    <t>JAHEL</t>
-  </si>
-  <si>
-    <t>VICTOR MANUEL</t>
-  </si>
-  <si>
-    <t>OMAR ALDAIR</t>
-  </si>
-  <si>
-    <t>CITLALLI</t>
+    <t>IVAN</t>
+  </si>
+  <si>
+    <t>JOSE EMMANUEL</t>
+  </si>
+  <si>
+    <t>KARLA</t>
   </si>
   <si>
     <t>DANIEL</t>
   </si>
   <si>
-    <t>ELIAN</t>
+    <t>ARIADNA</t>
   </si>
   <si>
     <t>ARANTZA</t>
   </si>
   <si>
     <t>ZULEICA RENATA</t>
-  </si>
-  <si>
-    <t>YAIR ANTONIO</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>MAURICIO</t>
-  </si>
-  <si>
-    <t>IVAN</t>
-  </si>
-  <si>
-    <t>URIEL</t>
-  </si>
-  <si>
-    <t>ALEXANDER</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>CRISTIAN</t>
-  </si>
-  <si>
-    <t>ALEXIS</t>
-  </si>
-  <si>
-    <t>ANGEL GERARDO</t>
-  </si>
-  <si>
-    <t>CESAR JAHIR</t>
-  </si>
-  <si>
-    <t>ARIAN ALEXIS</t>
-  </si>
-  <si>
-    <t>NAHOMY</t>
-  </si>
-  <si>
-    <t>NATANAEL</t>
-  </si>
-  <si>
-    <t>IRVING OTTONIEL</t>
   </si>
 </sst>
 </file>
@@ -753,10 +621,10 @@
         <v>24</v>
       </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
         <v>1</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
       </c>
       <c r="F5">
         <v>23</v>
@@ -765,7 +633,7 @@
         <v>95.83</v>
       </c>
       <c r="H5">
-        <v>7.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -948,19 +816,19 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>5</v>
       </c>
       <c r="F5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G5">
-        <v>75</v>
+        <v>79.17</v>
       </c>
       <c r="H5">
-        <v>7.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1068,16 +936,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G2">
-        <v>75</v>
+        <v>91.67</v>
       </c>
       <c r="H2">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1094,16 +962,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G3">
-        <v>69.7</v>
+        <v>87.88</v>
       </c>
       <c r="H3">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1120,16 +988,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="G4">
-        <v>65.79000000000001</v>
+        <v>86.84</v>
       </c>
       <c r="H4">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1143,19 +1011,19 @@
         <v>24</v>
       </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
         <v>1</v>
       </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
       <c r="F5">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G5">
-        <v>75</v>
+        <v>95.83</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1172,16 +1040,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G6">
-        <v>80.65000000000001</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1198,13 +1066,13 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F7">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G7">
-        <v>62.5</v>
+        <v>84.38</v>
       </c>
       <c r="H7">
         <v>6.3</v>
@@ -1217,7 +1085,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1249,22 +1117,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920381</v>
+        <v>19330051920040</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1272,22 +1140,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920354</v>
+        <v>19330051920247</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1295,22 +1163,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920382</v>
+        <v>19330051920265</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1318,39 +1186,39 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330050470596</v>
+        <v>20330051920287</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920285</v>
+        <v>20330051920297</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1359,21 +1227,21 @@
         <v>11</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920287</v>
+        <v>20330051920310</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1382,21 +1250,21 @@
         <v>11</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920298</v>
+        <v>20330051920379</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1405,397 +1273,6 @@
         <v>11</v>
       </c>
       <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920310</v>
-      </c>
-      <c r="B9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920379</v>
-      </c>
-      <c r="B10" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" t="s">
-        <v>48</v>
-      </c>
-      <c r="D10" t="s">
-        <v>70</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>18330051920168</v>
-      </c>
-      <c r="B11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" t="s">
-        <v>71</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>19330051920026</v>
-      </c>
-      <c r="B12" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" t="s">
-        <v>49</v>
-      </c>
-      <c r="D12" t="s">
-        <v>72</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>19330051920037</v>
-      </c>
-      <c r="B13" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" t="s">
-        <v>50</v>
-      </c>
-      <c r="D13" t="s">
-        <v>73</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>19330051920040</v>
-      </c>
-      <c r="B14" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" t="s">
-        <v>50</v>
-      </c>
-      <c r="D14" t="s">
-        <v>74</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>19330051920233</v>
-      </c>
-      <c r="B15" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" t="s">
-        <v>51</v>
-      </c>
-      <c r="D15" t="s">
-        <v>75</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>19330051420227</v>
-      </c>
-      <c r="B16" t="s">
-        <v>29</v>
-      </c>
-      <c r="C16" t="s">
-        <v>52</v>
-      </c>
-      <c r="D16" t="s">
-        <v>76</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>13</v>
-      </c>
-      <c r="G16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>19330051920251</v>
-      </c>
-      <c r="B17" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" t="s">
-        <v>53</v>
-      </c>
-      <c r="D17" t="s">
-        <v>77</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>15</v>
-      </c>
-      <c r="G17">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>19330051920433</v>
-      </c>
-      <c r="B18" t="s">
-        <v>37</v>
-      </c>
-      <c r="C18" t="s">
-        <v>54</v>
-      </c>
-      <c r="D18" t="s">
-        <v>78</v>
-      </c>
-      <c r="E18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" t="s">
-        <v>15</v>
-      </c>
-      <c r="G18">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>19330051920257</v>
-      </c>
-      <c r="B19" t="s">
-        <v>22</v>
-      </c>
-      <c r="C19" t="s">
-        <v>55</v>
-      </c>
-      <c r="D19" t="s">
-        <v>79</v>
-      </c>
-      <c r="E19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" t="s">
-        <v>15</v>
-      </c>
-      <c r="G19">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>19330051920400</v>
-      </c>
-      <c r="B20" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" t="s">
-        <v>56</v>
-      </c>
-      <c r="D20" t="s">
-        <v>80</v>
-      </c>
-      <c r="E20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" t="s">
-        <v>15</v>
-      </c>
-      <c r="G20">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>19330051920411</v>
-      </c>
-      <c r="B21" t="s">
-        <v>39</v>
-      </c>
-      <c r="C21" t="s">
-        <v>57</v>
-      </c>
-      <c r="D21" t="s">
-        <v>81</v>
-      </c>
-      <c r="E21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" t="s">
-        <v>15</v>
-      </c>
-      <c r="G21">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>19330051920001</v>
-      </c>
-      <c r="B22" t="s">
-        <v>40</v>
-      </c>
-      <c r="C22" t="s">
-        <v>58</v>
-      </c>
-      <c r="D22" t="s">
-        <v>82</v>
-      </c>
-      <c r="E22" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" t="s">
-        <v>14</v>
-      </c>
-      <c r="G22">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>19330051920208</v>
-      </c>
-      <c r="B23" t="s">
-        <v>41</v>
-      </c>
-      <c r="C23" t="s">
-        <v>59</v>
-      </c>
-      <c r="D23" t="s">
-        <v>83</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>11</v>
-      </c>
-      <c r="G23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>18330061460390</v>
-      </c>
-      <c r="B24" t="s">
-        <v>42</v>
-      </c>
-      <c r="C24" t="s">
-        <v>60</v>
-      </c>
-      <c r="D24" t="s">
-        <v>84</v>
-      </c>
-      <c r="E24" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" t="s">
-        <v>12</v>
-      </c>
-      <c r="G24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>19330051920088</v>
-      </c>
-      <c r="B25" t="s">
-        <v>43</v>
-      </c>
-      <c r="C25" t="s">
-        <v>61</v>
-      </c>
-      <c r="D25" t="s">
-        <v>85</v>
-      </c>
-      <c r="E25" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" t="s">
-        <v>14</v>
-      </c>
-      <c r="G25">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Ortega Valle Manuel - Estadisticos 20212.xlsx
+++ b/docentes/Ortega Valle Manuel - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="44">
   <si>
     <t>Mat</t>
   </si>
@@ -85,33 +85,36 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>BONILLA</t>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>SANTILLANA</t>
+  </si>
+  <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>TORRES</t>
   </si>
   <si>
     <t>MENDOZA</t>
   </si>
   <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
+    <t>SIERRA</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
@@ -124,25 +127,28 @@
     <t>CARRASCO</t>
   </si>
   <si>
-    <t>IVAN</t>
-  </si>
-  <si>
-    <t>JOSE EMMANUEL</t>
+    <t>YAMIL ELIEL</t>
+  </si>
+  <si>
+    <t>DIEGO ABDEL JARIN</t>
+  </si>
+  <si>
+    <t>CESAR GAEL</t>
+  </si>
+  <si>
+    <t>DANIEL</t>
+  </si>
+  <si>
+    <t>ARIADNA</t>
+  </si>
+  <si>
+    <t>ARANTZA</t>
+  </si>
+  <si>
+    <t>ZULEICA RENATA</t>
   </si>
   <si>
     <t>KARLA</t>
-  </si>
-  <si>
-    <t>DANIEL</t>
-  </si>
-  <si>
-    <t>ARIADNA</t>
-  </si>
-  <si>
-    <t>ARANTZA</t>
-  </si>
-  <si>
-    <t>ZULEICA RENATA</t>
   </si>
 </sst>
 </file>
@@ -1085,7 +1091,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1117,7 +1123,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920040</v>
+        <v>19330051920032</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
@@ -1126,7 +1132,7 @@
         <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -1140,7 +1146,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920247</v>
+        <v>19330051920259</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
@@ -1149,7 +1155,7 @@
         <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -1163,16 +1169,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920265</v>
+        <v>19330051920412</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -1192,10 +1198,10 @@
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1212,13 +1218,13 @@
         <v>20330051920297</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1235,13 +1241,13 @@
         <v>20330051920310</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1258,13 +1264,13 @@
         <v>20330051920379</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1273,6 +1279,29 @@
         <v>11</v>
       </c>
       <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>19330051920265</v>
+      </c>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9">
         <v>1</v>
       </c>
     </row>
